--- a/output/full_scan/batch_seq1_2026-06-23.xlsx
+++ b/output/full_scan/batch_seq1_2026-06-23.xlsx
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1342</v>
+        <v>1563</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>841.5760515592768</v>
+        <v>1008.670545530925</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>117</v>
+        <v>69.7</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>73.5028311573335</v>
+        <v>66.04575015969239</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>44.7475743522795</v>
+        <v>44.36430786476364</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.6138377210525299</v>
+        <v>1.854438975672293</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,11 +570,11 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.9938606502463738</v>
+        <v>-0.0345094607385974</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>820.5085636622755</v>
+        <v>990.5085636622756</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>28.55</v>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>66.21713941775879</v>
+        <v>66.21713943056218</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>32.41805168172278</v>
+        <v>32.41805168817649</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>2.538434125727986</v>
@@ -627,27 +627,27 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1563</v>
+        <v>1342</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>818.6705455309248</v>
+        <v>951.5760515592768</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>69.7</v>
+        <v>117</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>66.04575017948534</v>
+        <v>73.5028311795586</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>44.36430786234112</v>
+        <v>44.74757436671979</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.854438975672293</v>
+        <v>0.6138377210525299</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.0345094606767775</v>
+        <v>0.9938606501433488</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1303</v>
+        <v>1216</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>777.4563147861642</v>
+        <v>901.5666245484958</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>154.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>80.03260880496532</v>
+        <v>55.79944383105439</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>32.50143053597981</v>
+        <v>21.06718204142408</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.345631478616423</v>
+        <v>0.9563263076823244</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>5.209950436464389</v>
+        <v>0.009787744655586701</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1307</v>
+        <v>1210</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>738.1032714166437</v>
+        <v>867.0319248951655</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>35.05</v>
+        <v>54.6</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>55.65124902248101</v>
+        <v>54.90839056119253</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>29.99247953152161</v>
+        <v>28.18278708108172</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.01990964293403</v>
+        <v>0.4084657167650785</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.0733274378785167</v>
+        <v>0.0142228541820191</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1326</v>
+        <v>1513</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>731.5891559135306</v>
+        <v>851.8340799403494</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>53.1</v>
+        <v>182</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>56.22851394563728</v>
+        <v>65.93293053087557</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>23.49595833034716</v>
+        <v>21.24007792248497</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.29669637574785</v>
+        <v>0.8804952840225383</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4527636284225711</v>
+        <v>0.7234419117397657</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1203</v>
+        <v>1514</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>721.9670502959035</v>
+        <v>811.4355161918107</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>43.45</v>
+        <v>127</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>55.57366173971787</v>
+        <v>54.85542302953461</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>17.34066165915731</v>
+        <v>22.66950797641694</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.176618146409098</v>
+        <v>1.223897031969217</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.0152883637202002</v>
+        <v>-0.4368488471501457</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1216</v>
+        <v>1402</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>711.566624548496</v>
+        <v>804.5906265004963</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>75.09999999999999</v>
+        <v>28.65</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>55.79944375633183</v>
+        <v>61.10165379662342</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>21.06718202333072</v>
+        <v>18.72243454314135</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.9563263076823244</v>
+        <v>0.323160785527008</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.0097877446349856</v>
+        <v>0.18871268536872</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1210</v>
+        <v>1312</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>677.0319248951655</v>
+        <v>798.0248979609064</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>54.6</v>
+        <v>13.8</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>54.90839077199323</v>
+        <v>60.3134944589515</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>28.18278707788782</v>
+        <v>30.49784894778476</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.4084657167650785</v>
+        <v>0.6687918656816371</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.0142228538729342</v>
+        <v>0.073395121418539</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1446</v>
+        <v>1470</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>653.3200792964204</v>
+        <v>783.8915496563745</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>16.7</v>
+        <v>22.65</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>58.92272898144753</v>
+        <v>52.67291355778113</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>25.59256920285643</v>
+        <v>11.68204387744005</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.143234840586586</v>
+        <v>3.521266235094812</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.0060978916608442</v>
+        <v>0.1048429621532678</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1110</v>
+        <v>1303</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>632.5889735622447</v>
+        <v>777.4563147861642</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>15.55</v>
+        <v>154.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>56.96454951538767</v>
+        <v>80.03260880496532</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>33.30391476954393</v>
+        <v>32.50143053597981</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.4884484007551352</v>
+        <v>2.345631478616423</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.0220019164434806</v>
+        <v>5.209950436464389</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1312</v>
+        <v>1503</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>628.0248979609064</v>
+        <v>754.5728489898861</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13.8</v>
+        <v>242</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>60.31349441613263</v>
+        <v>60.97102604041058</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>30.49784894778476</v>
+        <v>21.48913884458782</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.6687918656816371</v>
+        <v>0.7456818496810707</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.0733951214700537</v>
+        <v>0.7331350162450647</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1560</v>
+        <v>1203</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>623.2422179895589</v>
+        <v>741.9670502959035</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>705</v>
+        <v>43.45</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>56.79249453194304</v>
+        <v>55.57366181603475</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>22.77640687063215</v>
+        <v>17.34066170417315</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.6462525287814666</v>
+        <v>1.176618146409098</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-1.573052755602362</v>
+        <v>0.015288363709892</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1443</v>
+        <v>1560</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>620.6952332271172</v>
+        <v>738.2422179895589</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>27.35</v>
+        <v>705</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,49 +1241,49 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>60.05050779231127</v>
+        <v>56.79249455416669</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>20.85074540565888</v>
+        <v>22.77640682181022</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.7611084067676321</v>
+        <v>0.6462525287814666</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.0578376596314796</v>
+        <v>-1.573052755705373</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1532</v>
+        <v>1307</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>614.820521761392</v>
+        <v>738.1032714166435</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>23.05</v>
+        <v>35.05</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>57.63400073846132</v>
+        <v>55.65124906400849</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>39.0637211936187</v>
+        <v>29.99247958310944</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.5685282673141204</v>
+        <v>1.01990964293403</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0755587716719681</v>
+        <v>0.073327438002148</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1503</v>
+        <v>1326</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>614.5728489898861</v>
+        <v>731.6594008646321</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>242</v>
+        <v>53.1</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>60.97102593073498</v>
+        <v>56.22851395579613</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>21.48913886744393</v>
+        <v>23.49595833034716</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.7456818496810707</v>
+        <v>1.311305265066654</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.7331350167602153</v>
+        <v>0.4527636283813565</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1513</v>
+        <v>1310</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>596.8340799403494</v>
+        <v>705.2633671633275</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>182</v>
+        <v>9.73</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>65.93293041894933</v>
+        <v>62.10835287767565</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>21.24007796490789</v>
+        <v>23.38331039476733</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.8804952840225383</v>
+        <v>2.437487180302284</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.7234419119458515</v>
+        <v>0.1765396329890578</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1456</v>
+        <v>1434</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>596.2729376025691</v>
+        <v>689.0738000040544</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>15</v>
+        <v>16.6</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>61.67053446852225</v>
+        <v>56.82196157042809</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>23.75403728685239</v>
+        <v>25.24026532686118</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.396586529638466</v>
+        <v>1.438600089209978</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.1855946763495226</v>
+        <v>0.0581395084836487</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1514</v>
+        <v>1568</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>586.4355161918107</v>
+        <v>685.0363562476593</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>127</v>
+        <v>44.85</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>54.85542288888971</v>
+        <v>60.83687243433686</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>22.66950801031729</v>
+        <v>45.00525488600697</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.223897031969217</v>
+        <v>1.045838815892546</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.4368488470677201</v>
+        <v>-0.2087067193320413</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1419</v>
+        <v>1515</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>579.6153396394702</v>
+        <v>674.4554424815387</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>66.5</v>
+        <v>26.8</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>54.57139008923131</v>
+        <v>65.56304504275238</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>21.09000393991097</v>
+        <v>27.48767005434415</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.6357803029090991</v>
+        <v>0.7455442481538755</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.0454007868917645</v>
+        <v>0.3898907369373795</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1434</v>
+        <v>1446</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>579.0738000040544</v>
+        <v>653.3200792964205</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>56.82196143194544</v>
+        <v>58.92272932940417</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>25.24026532453027</v>
+        <v>25.5925693609302</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.438600089209978</v>
+        <v>1.143234840586586</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.0581395085454681</v>
+        <v>0.0060978916299348</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1444</v>
+        <v>1110</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>577.7970401732883</v>
+        <v>652.5889735622447</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>6.92</v>
+        <v>15.55</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>55.30020504691257</v>
+        <v>56.96454970456805</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>31.75112527324845</v>
+        <v>33.30391500162015</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.4252858455384402</v>
+        <v>0.4884484007551352</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.0160685419187281</v>
+        <v>0.022001916474389</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1402</v>
+        <v>1437</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>574.5906265004963</v>
+        <v>647.484401250871</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>28.65</v>
+        <v>30.05</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>61.10165376535206</v>
+        <v>67.63007845510126</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>18.72243445963244</v>
+        <v>27.50838799310321</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.323160785527008</v>
+        <v>1.070852922402511</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.1887126852862969</v>
+        <v>0.152044575706922</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1423</v>
+        <v>1443</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>574.3534315154178</v>
+        <v>620.6952332271172</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>38.6</v>
+        <v>27.35</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>29.68529366434236</v>
+        <v>60.05050779799341</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>29.66620177870756</v>
+        <v>20.85074545766256</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.2257953876022681</v>
+        <v>0.7611084067676321</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.6695511466979748</v>
+        <v>0.057837659662393</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1568</v>
+        <v>1301</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>570.0363562476593</v>
+        <v>617.6160689911718</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>44.85</v>
+        <v>49.55</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,49 +1824,49 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>60.83687242612567</v>
+        <v>54.26286667279987</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45.00525489432515</v>
+        <v>19.96849384532201</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.045838815892546</v>
+        <v>0.8616068991171829</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.2087067192702267</v>
+        <v>0.5384069029630025</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1504</v>
+        <v>1532</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>569.6043259391912</v>
+        <v>614.820521761392</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>72.2</v>
+        <v>23.05</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>50.42629732331334</v>
+        <v>57.63400083761853</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>20.29777293315298</v>
+        <v>39.06372126789061</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.3428757029993616</v>
+        <v>0.5685282673141204</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.5918695909811934</v>
+        <v>0.07555877171318071</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1533</v>
+        <v>1102</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>564.2958331524299</v>
+        <v>599.237763653111</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>36.7</v>
+        <v>35.7</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>45.91982973090361</v>
+        <v>58.87428116304393</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>46.0092880824599</v>
+        <v>18.51300709426557</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7440211476051481</v>
+        <v>0.5969827725479937</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.3889832780262442</v>
+        <v>0.2310291030318734</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1313</v>
+        <v>1444</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>563.9894782169147</v>
+        <v>597.7970401732883</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>11.45</v>
+        <v>6.92</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>53.88877923310481</v>
+        <v>55.30020507371952</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>21.77943121602954</v>
+        <v>31.75112546439661</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.079162067261356</v>
+        <v>0.4252858455384402</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0903125589092888</v>
+        <v>-0.0160685419146067</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1470</v>
+        <v>1456</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>563.8915496563745</v>
+        <v>596.2729376025691</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>22.65</v>
+        <v>15</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>52.67291353971672</v>
+        <v>61.67053445451573</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>11.68204382936773</v>
+        <v>23.75403726953792</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>3.521266235094812</v>
+        <v>1.396586529638466</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.1048429622253899</v>
+        <v>0.1855946763701286</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1414</v>
+        <v>1504</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>539.0772785593465</v>
+        <v>589.6043259391912</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>17.45</v>
+        <v>72.2</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,49 +2089,49 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>63.3583393732597</v>
+        <v>50.42629736292162</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>25.23037356565792</v>
+        <v>20.2977728866681</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.7822689418649128</v>
+        <v>0.3428757029993616</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.1478761998298876</v>
+        <v>-0.5918695910017939</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1437</v>
+        <v>1419</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>537.4844012508704</v>
+        <v>579.6153396394699</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>30.05</v>
+        <v>66.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>67.63007824546068</v>
+        <v>54.57139021473604</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>27.50838799310321</v>
+        <v>21.09000395258664</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.070852922402511</v>
+        <v>0.6357803029090991</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.1520445757481316</v>
+        <v>0.0454007868196398</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1227</v>
+        <v>1423</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>525.7277208643619</v>
+        <v>574.3534315154178</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>29.15</v>
+        <v>38.6</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>57.51565073206413</v>
+        <v>29.68529362039419</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>18.6150769644447</v>
+        <v>29.66620178320799</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.3947895583137349</v>
+        <v>0.2257953876022681</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.1070537666410192</v>
+        <v>-0.6695511466155549</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1102</v>
+        <v>1447</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>524.237763653111</v>
+        <v>572.4085246701038</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>35.7</v>
+        <v>6.07</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>58.87428120029709</v>
+        <v>51.3101908633124</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>18.51300698220433</v>
+        <v>27.52910180696846</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.5969827725479937</v>
+        <v>0.5974786325443634</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.231029103011265</v>
+        <v>-0.08254710535719301</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1525</v>
+        <v>1236</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>520.3889848912942</v>
+        <v>571.3044123842488</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>65.8</v>
+        <v>25.85</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>51.03405539532648</v>
+        <v>64.13107351715439</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>28.53426041008637</v>
+        <v>14.90959043193706</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3013655555530238</v>
+        <v>0.5102400178987972</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.3533669265859969</v>
+        <v>0.09362441200824261</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1338</v>
+        <v>1533</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>511.8327765543252</v>
+        <v>564.2958331524299</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>16.75</v>
+        <v>36.7</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>51.96013244790777</v>
+        <v>45.91982948055117</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>21.24460037258972</v>
+        <v>46.00928769433623</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.9723997832654659</v>
+        <v>0.7440211476051481</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0206690236286802</v>
+        <v>-0.3889832774183754</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>505.2633671633276</v>
+        <v>563.9894782169147</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>9.73</v>
+        <v>11.45</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>62.10835283194459</v>
+        <v>53.8887792751329</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>23.3833103768827</v>
+        <v>21.77943121602954</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>2.437487180302284</v>
+        <v>1.079162067261356</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.1765396330137829</v>
+        <v>0.09031255888456199</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1314</v>
+        <v>1477</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>504.8946563839041</v>
+        <v>551.4694531988803</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>7.85</v>
+        <v>215</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>55.36725079530878</v>
+        <v>43.13111415526874</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>16.73995586942202</v>
+        <v>24.52487365019712</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.6566061230358012</v>
+        <v>1.78476653803551</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0112206083277795</v>
+        <v>-0.8268825460259938</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1515</v>
+        <v>1525</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>504.4554424815387</v>
+        <v>540.3889848912942</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>26.8</v>
+        <v>65.8</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>65.5630450584683</v>
+        <v>51.03405553691464</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>27.48766999156308</v>
+        <v>28.53426058041697</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.7455442481538755</v>
+        <v>0.3013655555530238</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.3898907368549554</v>
+        <v>-0.3533669268332694</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1301</v>
+        <v>1414</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>502.4855875620706</v>
+        <v>539.0772785593462</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>49.55</v>
+        <v>17.45</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>54.26286662206892</v>
+        <v>63.35833969772703</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>19.96849384532201</v>
+        <v>25.23037364040201</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.8485587562070569</v>
+        <v>0.7822689418649128</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.5384069030763315</v>
+        <v>0.1478761997769125</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1459</v>
+        <v>1225</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>500.4672563873527</v>
+        <v>537.7125243530289</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>11.8</v>
+        <v>30</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>52.67297061693988</v>
+        <v>46.37094818727214</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>14.04890801661319</v>
+        <v>20.18609193509215</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.506145367699351</v>
+        <v>0.7191665652251267</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0117242999704818</v>
+        <v>0.1648892361246587</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1104</v>
+        <v>1521</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>494.3431988626783</v>
+        <v>532.1010846657841</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>28.95</v>
+        <v>26.4</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>57.52737582610435</v>
+        <v>52.10413985128049</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>29.03842422319937</v>
+        <v>19.75221021830299</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2.334408546350707</v>
+        <v>0.1498408143408728</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0281921866927725</v>
+        <v>-0.087580578296543</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1455</v>
+        <v>1227</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>493.3511682890383</v>
+        <v>525.7277208643619</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>9.4</v>
+        <v>29.15</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>52.0061774442202</v>
+        <v>57.5156511489176</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>42.69720499085866</v>
+        <v>18.61507690788377</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.8802179352102008</v>
+        <v>0.3947895583137349</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.020267373812387</v>
+        <v>0.1070537665585963</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1323</v>
+        <v>1338</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>488.2108599516857</v>
+        <v>511.8327765543252</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>19.85</v>
+        <v>16.75</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>47.82320787485364</v>
+        <v>51.96013256794978</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>15.73113583468796</v>
+        <v>21.24460050719689</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6400755305517229</v>
+        <v>0.9723997832654659</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.002664610233759</v>
+        <v>0.0206690236286802</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1229</v>
+        <v>1314</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>487.235597280122</v>
+        <v>504.8946563839041</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>41.7</v>
+        <v>7.85</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>52.23317177658364</v>
+        <v>55.36725086487999</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>22.99184519678488</v>
+        <v>16.739955867153</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.8798622175820393</v>
+        <v>0.6566061230358012</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0451027009284538</v>
+        <v>0.0112206083236596</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1103</v>
+        <v>1459</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>475.1113170792664</v>
+        <v>500.4672563873527</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>13.65</v>
+        <v>11.8</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>55.69558142010978</v>
+        <v>52.67297106644718</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>15.14687858637106</v>
+        <v>14.04890801661319</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.6597128879275849</v>
+        <v>2.506145367699351</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0357248558681945</v>
+        <v>0.0117242998777567</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1225</v>
+        <v>1531</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>462.712524353029</v>
+        <v>499.0256373600464</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>30</v>
+        <v>12.9</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>46.37094818727214</v>
+        <v>54.89292343078237</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>20.18609193509215</v>
+        <v>17.95085553973147</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.7191665652251267</v>
+        <v>0.9789983911725416</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.1648892361246587</v>
+        <v>0.0199585321468023</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1447</v>
+        <v>1103</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>462.4085246701039</v>
+        <v>495.1113170792664</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>6.07</v>
+        <v>13.65</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>51.31019080725245</v>
+        <v>55.6955816549544</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>27.52910180236435</v>
+        <v>15.14687860038725</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.5974786325443634</v>
+        <v>0.6597128879275849</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0825471053510121</v>
+        <v>0.0357248558372848</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1236</v>
+        <v>1104</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>461.3044123842489</v>
+        <v>494.3431988626783</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>25.85</v>
+        <v>28.95</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>64.13107347497127</v>
+        <v>57.52737606883845</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>14.909590427869</v>
+        <v>29.03842422841894</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.5102400178987972</v>
+        <v>2.334408546350707</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.09362441199793869</v>
+        <v>0.0281921866309569</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>458.2403039269269</v>
+        <v>493.3511682890385</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>7.04</v>
+        <v>9.4</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>46.60718809454637</v>
+        <v>52.00617747857058</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>14.02322220848489</v>
+        <v>42.6972049935808</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.6460332041674566</v>
+        <v>0.8802179352102008</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.0091397374838423</v>
+        <v>-0.0202673738020842</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1215</v>
+        <v>1323</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>435.6077678028421</v>
+        <v>488.2108599516857</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>116</v>
+        <v>19.85</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>34.22895176392785</v>
+        <v>47.82320787485364</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>42.95331755806875</v>
+        <v>15.73113583468796</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.4135464523964383</v>
+        <v>0.6400755305517229</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.39923272225918</v>
+        <v>0.0026646102852738</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1519</v>
+        <v>1229</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>432.625510926789</v>
+        <v>487.235597280122</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>813</v>
+        <v>41.7</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,49 +3202,49 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>46.73055027503226</v>
+        <v>52.23317187163883</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>10.61835967204219</v>
+        <v>22.9918452169008</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4301375721402027</v>
+        <v>0.8798622175820393</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.2286546148777883</v>
+        <v>0.045102700907848</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1477</v>
+        <v>1435</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>431.4694531988803</v>
+        <v>463.2904119649982</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>215</v>
+        <v>17.05</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>43.13111411939736</v>
+        <v>54.39837516046776</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>24.52487362445508</v>
+        <v>8.118239774268083</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.78476653803551</v>
+        <v>0.3428015446811078</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.8268825456138709</v>
+        <v>0.9506917348524246</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>above_ema60, breakout_20d, market_above_ma60, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1474</v>
+        <v>1460</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>428.0668050265886</v>
+        <v>458.2403039269269</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>10.15</v>
+        <v>7.04</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>51.27888300669188</v>
+        <v>46.60718814946669</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>26.62920255189759</v>
+        <v>14.0232222298064</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.9719499195898348</v>
+        <v>0.6460332041674566</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0045308045581277</v>
+        <v>-0.009139737498265001</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1436</v>
+        <v>1475</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>425.5927619653563</v>
+        <v>456.8723630945854</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>45.35</v>
+        <v>27.3</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>43.61625244316077</v>
+        <v>58.09927289195946</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>26.84403469661999</v>
+        <v>19.6825897298441</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.8318967796746067</v>
+        <v>0.6958001502928324</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.2222915365708136</v>
+        <v>0.1917002007672077</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1521</v>
+        <v>1215</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>422.1010846657842</v>
+        <v>455.6077678028421</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>26.4</v>
+        <v>116</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>52.10413983559577</v>
+        <v>34.22895176392785</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>19.75221021830299</v>
+        <v>42.95331750976455</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.1498408143408728</v>
+        <v>0.4135464523964383</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.0875805781935152</v>
+        <v>0.3992327224652197</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1231</v>
+        <v>1530</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>421.4907598020428</v>
+        <v>453.3219285747476</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>88</v>
+        <v>28.95</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.3412311497141</v>
+        <v>39.96513373630178</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>19.83099470377825</v>
+        <v>25.98610619147811</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.9281808133752388</v>
+        <v>0.4568196742619095</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.1028385908575259</v>
+        <v>-0.485868265741856</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1321</v>
+        <v>1519</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>419.4791296689771</v>
+        <v>432.625510926789</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>30.55</v>
+        <v>813</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>50.61127183712559</v>
+        <v>46.73055036410425</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>42.19333387208773</v>
+        <v>10.61835961856335</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.180561816190076</v>
+        <v>0.4301375721402027</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.1868369281253304</v>
+        <v>0.2286546140535836</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1304</v>
+        <v>1516</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>405.8874893258049</v>
+        <v>428.3145545032403</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>12.8</v>
+        <v>19.85</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>47.29116585864826</v>
+        <v>38.14199680521508</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>17.71382193167888</v>
+        <v>17.35024253408828</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.03237360768347</v>
+        <v>0.6471784335361822</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0810412514078083</v>
+        <v>-0.1242564359863454</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1453</v>
+        <v>1474</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>400.3817306886351</v>
+        <v>428.0668050265886</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>11.55</v>
+        <v>10.15</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>49.75252655593968</v>
+        <v>51.27888311835467</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>28.66687588065268</v>
+        <v>26.62920255189759</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6297415998923666</v>
+        <v>0.9719499195898348</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0432859101408494</v>
+        <v>-0.004530804568431</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1517</v>
+        <v>1436</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>390.7860720430304</v>
+        <v>425.5927619653563</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>10.45</v>
+        <v>45.35</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>52.34498708077929</v>
+        <v>43.61625288209655</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>21.92775588688905</v>
+        <v>26.84403476074764</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.4108896076429599</v>
+        <v>0.8318967796746067</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0349946732431335</v>
+        <v>0.2222915365708136</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1531</v>
+        <v>1231</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>389.0256373600462</v>
+        <v>421.4907598020428</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>12.9</v>
+        <v>88</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>54.89292335344354</v>
+        <v>54.34123158267104</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>17.95085551348154</v>
+        <v>19.83099471205727</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.9789983911725416</v>
+        <v>0.9281808133752388</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0199585321261953</v>
+        <v>0.1028385905484371</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1432</v>
+        <v>1321</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>382.8514415779029</v>
+        <v>419.4791296689771</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>15.85</v>
+        <v>30.55</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>34.90132102457405</v>
+        <v>50.61127196689569</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>24.48896686372776</v>
+        <v>42.19333388072474</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>2.329907053840836</v>
+        <v>1.180561816190076</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.0380759358297289</v>
+        <v>0.1868369280841197</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1319</v>
+        <v>1213</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>381.7056587398807</v>
+        <v>418.9854541883507</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>79.40000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>38.02569392211845</v>
+        <v>50.77331810537935</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>33.53308894798093</v>
+        <v>10.39333947466533</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.716184393716995</v>
+        <v>1.864629426659088</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-2.25215413603537</v>
+        <v>0.1614696117454257</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1522</v>
+        <v>1319</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>381.6982622853366</v>
+        <v>411.7056587398807</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>30.45</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>44.39439586550775</v>
+        <v>38.02569396358752</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>15.27387724258655</v>
+        <v>33.53308897473913</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.5283253735697043</v>
+        <v>1.716184393716995</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0228584527912362</v>
+        <v>-2.252154136550504</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1418</v>
+        <v>1517</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>379.7686503700085</v>
+        <v>410.7860720430304</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>18</v>
+        <v>10.45</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>42.24538652069045</v>
+        <v>52.34498712751294</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>22.8212531742867</v>
+        <v>21.92775589226322</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.875562958275952</v>
+        <v>0.4108896076429599</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0631725506480358</v>
+        <v>0.0349946732328311</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1305</v>
+        <v>1538</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>372.1626325101877</v>
+        <v>409.74257314219</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>12.65</v>
+        <v>11.8</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>45.44333877723378</v>
+        <v>51.79145328622443</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>11.82245099972963</v>
+        <v>5.827128043320249</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.9738376360319796</v>
+        <v>1.389780724898437</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0843112543325225</v>
+        <v>-0.0106244103304645</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1339</v>
+        <v>1453</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>367.6662164381657</v>
+        <v>400.3817306886351</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>43.8</v>
+        <v>11.55</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>53.93960309305912</v>
+        <v>49.75252704050981</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>22.65207360811101</v>
+        <v>28.66687592290217</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3578417626174709</v>
+        <v>0.6297415998923666</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.1049996723589761</v>
+        <v>0.0432859100584265</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1315</v>
+        <v>1476</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>362.4520011584422</v>
+        <v>395.9272010744389</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>62.4</v>
+        <v>312.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,49 +4103,49 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>57.39715726705624</v>
+        <v>34.1767935682617</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>13.6128068144369</v>
+        <v>16.47705876455651</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.161081212755496</v>
+        <v>0.9927201074438852</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M69" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.1492514155197331</v>
+        <v>-3.902131854408332</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1219</v>
+        <v>1304</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>361.1298428542418</v>
+        <v>395.8874893258049</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>12.45</v>
+        <v>12.8</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>37.28247621281312</v>
+        <v>47.29116591980046</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>28.02752060874671</v>
+        <v>17.71382194045929</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.977929646426966</v>
+        <v>1.03237360768347</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0210469320482309</v>
+        <v>0.0810412513562933</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1440</v>
+        <v>1527</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>355.7079195533974</v>
+        <v>394.4672153089736</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>13.4</v>
+        <v>33.05</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>54.13446422311978</v>
+        <v>49.46918564716275</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>23.05633040608949</v>
+        <v>17.15328284918717</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.2940117436938911</v>
+        <v>1.668825525967145</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.0274266731947034</v>
+        <v>-0.0356960858304801</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1537</v>
+        <v>1529</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>355.5306165753679</v>
+        <v>390.9232392686051</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>125.5</v>
+        <v>22.95</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45.52051486599989</v>
+        <v>52.7395791357177</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>11.00662146890167</v>
+        <v>16.93803923105853</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.443930172382375</v>
+        <v>0.5234760351037648</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.1611387799699118</v>
+        <v>0.0202402358278157</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1524</v>
+        <v>1432</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>350.5505704095884</v>
+        <v>382.8514415779029</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>28.95</v>
+        <v>15.85</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>42.37663897885642</v>
+        <v>34.90132109982184</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>14.96605618039162</v>
+        <v>24.48896686980117</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.3327164052083917</v>
+        <v>2.329907053840836</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.2875191527582049</v>
+        <v>-0.0380759358400339</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1475</v>
+        <v>1522</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>346.8723630945853</v>
+        <v>381.6982622853365</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>27.3</v>
+        <v>30.45</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>58.09927267505974</v>
+        <v>44.39439598026124</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>19.6825897435471</v>
+        <v>15.27387743476417</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.6958001502928324</v>
+        <v>0.5283253735697043</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.1917002009732682</v>
+        <v>-0.0228584528736594</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1528</v>
+        <v>1418</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>345.4736292812661</v>
+        <v>379.7686503700085</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>24.9</v>
+        <v>18</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>42.93018864417273</v>
+        <v>42.24538671472946</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>8.002226485203737</v>
+        <v>22.8212531742867</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5037219946742776</v>
+        <v>0.875562958275952</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.1654851237345827</v>
+        <v>-0.0631725506892504</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1256</v>
+        <v>1305</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>344.4351083795497</v>
+        <v>372.1626325101877</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>180</v>
+        <v>12.65</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>47.76845575628978</v>
+        <v>45.44333882753728</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>19.81759767150228</v>
+        <v>11.82245102976432</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.8162129456607372</v>
+        <v>0.9738376360319796</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-1.573749928552792</v>
+        <v>0.0843112542810075</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1464</v>
+        <v>1339</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>343.4234154065544</v>
+        <v>367.6662164381657</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>10.15</v>
+        <v>43.8</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>43.07387630484182</v>
+        <v>53.93960322440604</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>20.13300120916873</v>
+        <v>22.65207361071664</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.201617874268514</v>
+        <v>0.3578417626174709</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0293467501164568</v>
+        <v>-0.1049996725650341</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1530</v>
+        <v>1535</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>343.3219285747476</v>
+        <v>367.5895714230016</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>28.95</v>
+        <v>50</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>39.96513370086794</v>
+        <v>49.06760299108662</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>25.98610599473683</v>
+        <v>25.82632850798078</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.4568196742619095</v>
+        <v>0.6456474750981951</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.4858682657624612</v>
+        <v>0.0570800827997186</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1538</v>
+        <v>1315</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>334.74257314219</v>
+        <v>362.4520011584421</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>11.8</v>
+        <v>62.4</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>51.79145328622443</v>
+        <v>57.39715739120357</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>5.827128038684599</v>
+        <v>13.6128068666929</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.389780724898437</v>
+        <v>1.161081212755496</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0106244103304645</v>
+        <v>0.1492514154167045</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>326.1968933306049</v>
+        <v>361.1298428542418</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>9.85</v>
+        <v>12.45</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>52.23278317900409</v>
+        <v>37.28247671860094</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>21.32418637774335</v>
+        <v>28.0275206952983</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.5885158172368139</v>
+        <v>0.977929646426966</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0093573079988997</v>
+        <v>0.0210469321100491</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4714,21 +4714,21 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1472</v>
+        <v>1440</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>322.6883699948445</v>
+        <v>355.7079195533974</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>89</v>
+        <v>13.4</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>50.26566516451066</v>
+        <v>54.1344644661184</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>8.558075632687551</v>
+        <v>23.05633042965272</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.06883699948444751</v>
+        <v>0.2940117436938911</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.1234789995173119</v>
+        <v>-0.0274266732359153</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1451</v>
+        <v>1537</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>322.628644998217</v>
+        <v>355.5306165753679</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>16.8</v>
+        <v>125.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>51.31374648962694</v>
+        <v>45.52051500337402</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>10.71809321514716</v>
+        <v>11.00662151266739</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.6819108323818338</v>
+        <v>1.443930172382375</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.039015505199352</v>
+        <v>-0.1611387799699118</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1442</v>
+        <v>1524</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>320.3240130647305</v>
+        <v>350.5505704095885</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>27.35</v>
+        <v>28.95</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>51.56013047049713</v>
+        <v>42.37663911465099</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>22.2343465936541</v>
+        <v>14.96605635012702</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3872034481648053</v>
+        <v>0.3327164052083917</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.0508898837488716</v>
+        <v>-0.287519152850931</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1516</v>
+        <v>1528</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>318.3145545032404</v>
+        <v>345.4736292812661</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>19.85</v>
+        <v>24.9</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>38.1419966576933</v>
+        <v>42.93018857194137</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>17.35024253227099</v>
+        <v>8.002226348694148</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6471784335361822</v>
+        <v>0.5037219946742776</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.1242564359245283</v>
+        <v>-0.1654851236109458</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1506</v>
+        <v>1256</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>317.9359862824584</v>
+        <v>344.4351083795497</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>10.1</v>
+        <v>180</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>43.50009563806137</v>
+        <v>47.76845578566854</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>26.19564885743391</v>
+        <v>19.81759765513569</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.075635409429034</v>
+        <v>0.8162129456607372</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0203439958399966</v>
+        <v>-1.573749928861875</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1526</v>
+        <v>1464</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>313.1503231532176</v>
+        <v>343.4234154065544</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>14.4</v>
+        <v>10.15</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>40.61822125139665</v>
+        <v>43.07387651200729</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>21.43245394136936</v>
+        <v>20.13300127487858</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.6952482695100302</v>
+        <v>1.201617874268514</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0361709747048956</v>
+        <v>-0.0293467501370619</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1465</v>
+        <v>1413</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>308.1340194336018</v>
+        <v>330.2800418958202</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>12.45</v>
+        <v>9.35</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>54.8113884227604</v>
+        <v>47.38972111305358</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>12.96376942060239</v>
+        <v>8.251135677373512</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.6747284013114596</v>
+        <v>0.7517801101321273</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0051837161353911</v>
+        <v>-0.0205097420286369</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1308</v>
+        <v>1217</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>304.8567251719102</v>
+        <v>326.1968933306049</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>13.6</v>
+        <v>9.85</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>47.71544620298098</v>
+        <v>52.23278323857814</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>14.83399779317026</v>
+        <v>21.32418637774335</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.9453815535449512</v>
+        <v>0.5885158172368139</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.08352228672470891</v>
+        <v>0.0093573079988997</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1466</v>
+        <v>1472</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>300.340164597337</v>
+        <v>322.6883699948445</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>14.4</v>
+        <v>89</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>46.71475278740923</v>
+        <v>50.26566529346681</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>15.29058644003366</v>
+        <v>8.558075895735286</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6943126756516056</v>
+        <v>0.06883699948444751</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.07875925652092459</v>
+        <v>0.1234789977657997</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1512</v>
+        <v>1451</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>286.4217764077824</v>
+        <v>322.6286449982171</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>6.76</v>
+        <v>16.8</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>42.33443180911532</v>
+        <v>51.31374674609857</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>10.17774047092191</v>
+        <v>10.71809324640979</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.6685821376616365</v>
+        <v>0.6819108323818338</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0121850043414518</v>
+        <v>0.0390155051787437</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1527</v>
+        <v>1442</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>284.4672153089735</v>
+        <v>320.3240130647305</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>33.05</v>
+        <v>27.35</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>49.46918552009789</v>
+        <v>51.5601305409746</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>17.15328283704342</v>
+        <v>22.23434683445436</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.668825525967145</v>
+        <v>0.3872034481648053</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.0356960857995694</v>
+        <v>0.050889883996139</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1218</v>
+        <v>1506</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>283.1839952346862</v>
+        <v>317.9359862824584</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>17.85</v>
+        <v>10.1</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>31.2579918117025</v>
+        <v>43.50009555583965</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>30.40563788682883</v>
+        <v>26.19564897874121</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4143173663196114</v>
+        <v>1.075635409429034</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.1439383282856401</v>
+        <v>0.020343995870906</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1201</v>
+        <v>1526</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>282.7152335639186</v>
+        <v>313.1503231532176</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>12.35</v>
+        <v>14.4</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>47.63577034151808</v>
+        <v>40.61822131764582</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>22.58502755944739</v>
+        <v>21.43245400298482</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.8735880462988198</v>
+        <v>0.6952482695100302</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0269161842974539</v>
+        <v>0.0361709746636845</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1529</v>
+        <v>1465</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>280.9232392686061</v>
+        <v>308.1340194336018</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>22.95</v>
+        <v>12.45</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>52.73957884615933</v>
+        <v>54.81138851657112</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>16.93803917344475</v>
+        <v>12.96376941226761</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5234760351037648</v>
+        <v>0.6747284013114596</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0202402358999355</v>
+        <v>0.0051837161250904</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1341</v>
+        <v>1512</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>280.1304786561568</v>
+        <v>306.4217764077823</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>59</v>
+        <v>6.76</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>33.46072877849456</v>
+        <v>42.33443190713446</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>12.8652291318504</v>
+        <v>10.17774043289523</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.808886481575315</v>
+        <v>0.6685821376616365</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.315274675685923</v>
+        <v>0.0121850043229073</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1454</v>
+        <v>1308</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>276.7967572115472</v>
+        <v>304.8567251719102</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>12.9</v>
+        <v>13.6</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>48.62327156013117</v>
+        <v>47.71544629430234</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>23.33928657215447</v>
+        <v>14.83399784246668</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.2965098144946843</v>
+        <v>0.9453815535449512</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0138817162907107</v>
+        <v>0.08352228665258871</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1558</v>
+        <v>1466</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>276.225715211991</v>
+        <v>300.3401645973212</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>91.2</v>
+        <v>14.4</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>51.33744034303702</v>
+        <v>46.71475291439634</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>12.87181048748646</v>
+        <v>15.29058654021834</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.7866571344913639</v>
+        <v>0.6943126756516056</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0966179251937487</v>
+        <v>0.0787592564385005</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1438</v>
+        <v>1454</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>268.9353078811566</v>
+        <v>296.7967572115472</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>21.3</v>
+        <v>12.9</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>46.47842559222193</v>
+        <v>48.62327156013117</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>25.08630568446647</v>
+        <v>23.33928664551501</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.2758274877026934</v>
+        <v>0.2965098144946843</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.1727666635786891</v>
+        <v>0.013881716280407</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1109</v>
+        <v>1438</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>268.896694780342</v>
+        <v>288.9353078811566</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>14.4</v>
+        <v>21.3</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>33.64600009868184</v>
+        <v>46.47842567998831</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>23.60964649578193</v>
+        <v>25.08630568446647</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.751647854310826</v>
+        <v>0.2758274877026934</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0008398581868605</v>
+        <v>0.172766663640508</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1476</v>
+        <v>1218</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>265.9272010744388</v>
+        <v>283.1839952346861</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>312.5</v>
+        <v>17.85</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>34.17679378232312</v>
+        <v>31.25799190564889</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>16.47705877376075</v>
+        <v>30.40563787765084</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.9927201074438852</v>
+        <v>0.4143173663196114</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-3.902131857499248</v>
+        <v>-0.143938328306246</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1435</v>
+        <v>1201</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>263.2904119649982</v>
+        <v>282.7152335639186</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>17.05</v>
+        <v>12.35</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>54.39837527987653</v>
+        <v>47.63577068110048</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>8.118239149289407</v>
+        <v>22.58502756769197</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.3428015446811078</v>
+        <v>0.8735880462988198</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,28 +5817,28 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.95069173412687</v>
+        <v>0.0269161842871517</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, breakout_20d, market_above_ma60, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>260.8162638141948</v>
+        <v>282.4080929171803</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>21.85</v>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>50.91344714715178</v>
+        <v>51.08486494548676</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>14.30861142786731</v>
+        <v>13.9175630601927</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.643436400166266</v>
+        <v>0.3098560079698343</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0329808436477219</v>
+        <v>0.1901011739919574</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1535</v>
+        <v>1341</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>257.5895714230016</v>
+        <v>280.1304786561567</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>49.0676029250746</v>
+        <v>33.46072868031928</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>25.82632845614347</v>
+        <v>12.86522914334465</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.6456474750981951</v>
+        <v>1.808886481575315</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0570800827997186</v>
+        <v>-0.3152746755004647</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1467</v>
+        <v>1558</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>245.9540320594264</v>
+        <v>276.225715211991</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>7.11</v>
+        <v>91.2</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>41.07451151327155</v>
+        <v>51.33744042182862</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>25.76583171468313</v>
+        <v>12.87181053825402</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3383254629794952</v>
+        <v>0.7866571344913639</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0587641868894189</v>
+        <v>0.0966179251731486</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1101</v>
+        <v>1109</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>241.7934556914073</v>
+        <v>268.896694780342</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>24.15</v>
+        <v>14.4</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>46.16808805591226</v>
+        <v>33.64600018860455</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>13.647811374221</v>
+        <v>23.60964661969128</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.9812619393960538</v>
+        <v>1.751647854310826</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.008269019322700201</v>
+        <v>0.0008398581971637</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1232</v>
+        <v>1467</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>239.3468079892448</v>
+        <v>265.9540320594264</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>142</v>
+        <v>7.11</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>28.24584006570528</v>
+        <v>41.0745115877641</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>27.60854861972939</v>
+        <v>25.76583177056651</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.834680798924484</v>
+        <v>0.3383254629794952</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.718072097052689</v>
+        <v>-0.058764186916207</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1452</v>
+        <v>1540</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>235.3591583167785</v>
+        <v>260.8162638141946</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>10.95</v>
+        <v>21.85</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>50.61040840445925</v>
+        <v>50.91344712882579</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>17.62682716016459</v>
+        <v>14.30861155518738</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.8146618844217478</v>
+        <v>0.643436400166266</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0402234933914192</v>
+        <v>-0.0329808433592428</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1416</v>
+        <v>1410</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>224.5075791535628</v>
+        <v>242.2413923738902</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>10.9</v>
+        <v>24.65</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>40.11274564941551</v>
+        <v>32.59452291221531</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>24.60144326156295</v>
+        <v>16.13393707787606</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.5501164473751525</v>
+        <v>0.8785437821288429</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0347549447650404</v>
+        <v>0.0441465689374347</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1536</v>
+        <v>1101</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>220.4955097332757</v>
+        <v>241.7934556914073</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>49</v>
+        <v>24.15</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>45.54489818217945</v>
+        <v>46.16808809367373</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>13.1730991531379</v>
+        <v>13.64781142067193</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.9469957662121848</v>
+        <v>0.9812619393960538</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0069395313746575</v>
+        <v>0.008269019353608201</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1413</v>
+        <v>1232</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>220.28004189582</v>
+        <v>239.3468079892448</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>9.35</v>
+        <v>142</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>47.38972103578495</v>
+        <v>28.24584026705241</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>8.251135507650801</v>
+        <v>27.60854863214568</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.7517801101321273</v>
+        <v>0.834680798924484</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0205097420492416</v>
+        <v>-0.7180720971557268</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1213</v>
+        <v>1452</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>218.9854541883508</v>
+        <v>235.3591583167785</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>8.09</v>
+        <v>10.95</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>50.77331809858332</v>
+        <v>50.61040855432688</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>10.39333944582732</v>
+        <v>17.62682716016459</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.864629426659088</v>
+        <v>0.8146618844217478</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.1614696117763341</v>
+        <v>0.040223493381116</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>216.3558780170828</v>
+        <v>227.5065467746074</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>19.85</v>
+        <v>10.9</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>34.01915481121893</v>
+        <v>47.71902546776303</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>21.15826008944557</v>
+        <v>13.48799578296093</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.447795838438553</v>
+        <v>0.5561651807696617</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0553434418116858</v>
+        <v>0.0075154949257593</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1309</v>
+        <v>1416</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>213.6269659655272</v>
+        <v>224.5075791535628</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>14.4</v>
+        <v>10.9</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>38.71258476519877</v>
+        <v>40.11274606542544</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>11.4762714194899</v>
+        <v>24.60144327193319</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5642906391438303</v>
+        <v>0.5501164473751525</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0003137539402623</v>
+        <v>-0.034754944775344</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1316</v>
+        <v>1536</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>211.5988514421053</v>
+        <v>220.4955097332758</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>10.3</v>
+        <v>49</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>41.48431072992368</v>
+        <v>45.54489821647808</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>18.01152528937042</v>
+        <v>13.17309924814197</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.5965230783628667</v>
+        <v>0.9469957662121848</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.017932707329679</v>
+        <v>0.0069395318073743</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1324</v>
+        <v>1473</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>210.5155661065492</v>
+        <v>216.3558780170828</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>10.35</v>
+        <v>19.85</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>45.05302306192246</v>
+        <v>34.01915491123984</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>20.46734102026223</v>
+        <v>21.15826034088313</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.063185647704082</v>
+        <v>1.447795838438553</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.002091342054471</v>
+        <v>-0.0553434417292612</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,21 +6569,21 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1471</v>
+        <v>1316</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>207.5065467746074</v>
+        <v>211.5988514421052</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>47.7190256711779</v>
+        <v>41.48431120966704</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>13.48799523977854</v>
+        <v>18.0115252887407</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.5561651807696617</v>
+        <v>0.5965230783628667</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0075154947279426</v>
+        <v>0.0179327072575589</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1582</v>
+        <v>1324</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>195.2200648011959</v>
+        <v>210.5155661065492</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>90.5</v>
+        <v>10.35</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>41.11214576065333</v>
+        <v>45.05302315119332</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>19.59997738965789</v>
+        <v>20.46734096457305</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.4088032276083865</v>
+        <v>1.063185647704082</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-1.277604021964212</v>
+        <v>-0.002091342054471</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1108</v>
+        <v>1309</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>188.5137897367756</v>
+        <v>203.6269659655272</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>46.06156277049001</v>
+        <v>38.71258479527665</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>27.99296210119159</v>
+        <v>11.4762714194899</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.6662157099289466</v>
+        <v>0.5642906391438303</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0424461179861483</v>
+        <v>-0.0003137539608676</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1220</v>
+        <v>1233</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>188.2018729884189</v>
+        <v>200.5371072817573</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>11.7</v>
+        <v>28.1</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>38.38382357076729</v>
+        <v>49.58045518919533</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>29.05025468779877</v>
+        <v>16.51438513630985</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.7043389007962276</v>
+        <v>0.2644607575027421</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.0211220347564318</v>
+        <v>0.0778971842355118</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1439</v>
+        <v>1582</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>181.528450623495</v>
+        <v>195.2200648011959</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>24.25</v>
+        <v>90.5</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>44.32582300376699</v>
+        <v>41.11214579637176</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>6.607523943828173</v>
+        <v>19.59997740561957</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.304454451059478</v>
+        <v>0.4088032276083865</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.0924966494091299</v>
+        <v>-1.277604022293896</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1233</v>
+        <v>1108</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>180.5371072817573</v>
+        <v>188.5137897367756</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>28.1</v>
+        <v>13.8</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>49.58045536277284</v>
+        <v>46.06156324277449</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>16.51438499836777</v>
+        <v>27.99296210119161</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.2644607575027421</v>
+        <v>0.6662157099289466</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0778971841530896</v>
+        <v>0.0424461179655435</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1457</v>
+        <v>1220</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>169.8438014966325</v>
+        <v>188.2018729884189</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>14.15</v>
+        <v>11.7</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>42.37706685819171</v>
+        <v>38.38382394073782</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>18.0313658781622</v>
+        <v>29.05025485448398</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.3772376573505764</v>
+        <v>0.7043389007962276</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.0422404973395066</v>
+        <v>0.0211220347873409</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1340</v>
+        <v>1439</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>168.0829452960549</v>
+        <v>181.528450623495</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>5.47</v>
+        <v>24.25</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>41.68236328738001</v>
+        <v>44.32582300820633</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>15.05325994898538</v>
+        <v>6.607523978294979</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.3445455068478432</v>
+        <v>1.304454451059478</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.006613685226458</v>
+        <v>-0.09249664939882871</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1541</v>
+        <v>1457</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>167.4080929171803</v>
+        <v>169.8438014966326</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>21.85</v>
+        <v>14.15</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>51.0848648387643</v>
+        <v>42.37706703089506</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>13.91756300990732</v>
+        <v>18.0313658781622</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.3098560079698343</v>
+        <v>0.3772376573505764</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.1901011740743842</v>
+        <v>-0.0422404973601128</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1417</v>
+        <v>1340</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>145.0847475041757</v>
+        <v>168.0829452960549</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>8.369999999999999</v>
+        <v>5.47</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>44.11982419793984</v>
+        <v>41.68236329376293</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>17.20911935923086</v>
+        <v>15.05325983385995</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.8597473433023686</v>
+        <v>0.3445455068478432</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.0166048639953405</v>
+        <v>0.006613685226458</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1463</v>
+        <v>1417</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>138.050886184643</v>
+        <v>145.0847475041757</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>17.35</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>34.86388844589179</v>
+        <v>44.1198243703119</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>15.51259877528159</v>
+        <v>17.20911937279164</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.6396536264612115</v>
+        <v>0.8597473433023686</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.0212376223327542</v>
+        <v>0.0166048639974014</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1410</v>
+        <v>1463</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>132.2413923738902</v>
+        <v>138.0508861846417</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>24.65</v>
+        <v>17.35</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>32.59452271874008</v>
+        <v>34.86388951933061</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>16.13393713730957</v>
+        <v>15.51259876852281</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.8785437821288429</v>
+        <v>0.6396536264612115</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.0441465689374347</v>
+        <v>-0.0212376223842706</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>36.82425267965753</v>
+        <v>36.82425264900898</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>15.07455550027361</v>
+        <v>15.07455548779556</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>0.9753133540349318</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.09843799691707381</v>
+        <v>-0.0984379967831321</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>117.3466034179088</v>
+        <v>117.3466034179089</v>
       </c>
       <c r="E129" s="2" t="n">
         <v>9.07</v>
@@ -7283,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>38.28935158078171</v>
+        <v>38.28935068495628</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>16.12969005286895</v>
+        <v>16.12969126919141</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>1.030213166366255</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" s="2" t="n">
         <v>0</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.0152330511233495</v>
+        <v>0.0152330513603144</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7311,21 +7311,21 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>1325</v>
+        <v>1468</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>83.43943393498715</v>
+        <v>94.14471538957062</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>25.75</v>
+        <v>11.95</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,16 +7336,16 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>41.040568812021</v>
+        <v>47.49013597605057</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>13.96833085333165</v>
+        <v>8.086435119666916</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.7733494723662634</v>
+        <v>0.8957271018096487</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L130" s="2" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.07285177290600971</v>
+        <v>0.0151563386458978</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7364,21 +7364,21 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>1445</v>
+        <v>1325</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>74.18397925003973</v>
+        <v>83.43943393498658</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>10.65</v>
+        <v>25.75</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,16 +7389,16 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>25.50658341158706</v>
+        <v>41.04056823130679</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>19.68100771459476</v>
+        <v>13.96833082598472</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.6548751623685007</v>
+        <v>0.7733494723662634</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" s="2" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.0344394296040446</v>
+        <v>-0.0728517723805643</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>1468</v>
+        <v>1445</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>74.14471538957059</v>
+        <v>74.18397925003993</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>11.95</v>
+        <v>10.65</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>47.49013587577251</v>
+        <v>25.50658349740073</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>8.086435028215957</v>
+        <v>19.6810076759367</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.8957271018096487</v>
+        <v>0.6548751623685007</v>
       </c>
       <c r="K132" s="2" t="n">
         <v>0</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.0151563386252924</v>
+        <v>-0.0344394296246501</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>44.48317921597763</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>16.49698450407443</v>
+        <v>16.49698468774232</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>0.4033766202703141</v>
